--- a/model_analysis/small_qf_multiple_single_variable_analysis.xlsx
+++ b/model_analysis/small_qf_multiple_single_variable_analysis.xlsx
@@ -1,203 +1,240 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25460" windowHeight="12700" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="17830" firstSheet="7" activeTab="7"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Diameter of basal phase" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Width of basal phase" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Diameter of prismatic phase" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Diameter of basal phase_max_change_Yield Strength" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Width of basal phase_max_change_Yield Strength" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Diameter of prismatic phase_max_change_Yield Strength" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Fraction of basal phase_max_change_Yield Strength" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Fraction of prismatic phase_max_change_Yield Strength" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Width of prismatic phase_max_change_Yield Strength" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Diameter of basal phase" sheetId="2" r:id="rId2"/>
+    <sheet name="Width of basal phase" sheetId="3" r:id="rId3"/>
+    <sheet name="Diameter of prismatic phase" sheetId="4" r:id="rId4"/>
+    <sheet name="Diameter of basal phase_max_cha" sheetId="5" r:id="rId5"/>
+    <sheet name="Width of basal phase_max_change" sheetId="6" r:id="rId6"/>
+    <sheet name="Diameter of prismatic phase_max" sheetId="7" r:id="rId7"/>
+    <sheet name="Fraction of basal phase_max_cha" sheetId="8" r:id="rId8"/>
+    <sheet name="Fraction of prismatic phase_max" sheetId="9" r:id="rId9"/>
+    <sheet name="Width of prismatic phase_max_ch" sheetId="10" r:id="rId10"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="8">
+  <si>
+    <t>Track Number</t>
+  </si>
+  <si>
+    <t>Diameter of basal phase with Max Change</t>
+  </si>
+  <si>
+    <t>Predicted Yield Strength</t>
+  </si>
+  <si>
+    <t>Width of basal phase with Max Change</t>
+  </si>
+  <si>
+    <t>Diameter of prismatic phase with Max Change</t>
+  </si>
+  <si>
+    <t>Fraction of basal phase with Max Change</t>
+  </si>
+  <si>
+    <t>Fraction of prismatic phase with Max Change</t>
+  </si>
+  <si>
+    <t>Width of prismatic phase with Max Change</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -389,7 +426,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -510,166 +547,157 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -725,74 +753,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1079,4682 +1044,4635 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="50.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Width of prismatic phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>6</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>384.188</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>6</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>427.68</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>6</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>425.2</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>6</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>431.138</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>50</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>149.544</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>36</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>165.83</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>50</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>245.33</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>50</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>218.226</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>6</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>425.404</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>6</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>453.694</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>6</v>
       </c>
-      <c r="C12" t="n">
-        <v>459.4920000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="C12">
+        <v>459.492</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>6</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>504.432</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>6</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>449.708</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>6</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>454.42</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>8</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>317.196</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>8</v>
       </c>
-      <c r="C17" t="n">
-        <v>337.8220000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="C17">
+        <v>337.822</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>8</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>334.08</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>8</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>355.186</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>8</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>357.136</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>8</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>356.88</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>285.672</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>259.85</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>271.118</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>50</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>186.876</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>50</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>203.4</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>50</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>194.712</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>50</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>211.424</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>290.776</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>284.664</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>280.872</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>50</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>177.5</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>50</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>183.836</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>50</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>180.432</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>50</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>187.106</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>50</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>161.326</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>50</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>203.662</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>50</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>225.652</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>50</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>191.982</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>50</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>207.8</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>50</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>209.436</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>50</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>210.422</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>50</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>213.036</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>36</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>243.614</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>6</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>430.86</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>6</v>
       </c>
-      <c r="C46" t="n">
-        <v>462.1900000000001</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="C46">
+        <v>462.19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>6</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>500.298</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>8</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>378.522</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>50</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>177.288</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>50</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>151.902</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>6</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>200.504</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>50</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>187.27</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>6</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>200.504</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>50</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>187.27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="49.125" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Diameter of basal phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>38</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>385.678</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>38</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>425.788</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>5</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>26</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>156.616</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>28</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>245.698</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>38</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>426.27</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>11</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>38</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>467.756</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>13</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>38</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>447.672</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>15</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>10</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>315.606</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>17</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>38</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>332.804</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>19</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>26</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>360.058</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>21</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>28</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>283.13</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>23</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>28</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>267.886</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>25</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>28</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>210.768</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>27</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>28</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>219.028</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>29</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>279.72</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>31</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>27</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>183.366</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>33</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>38</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>182.002</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>35</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>26</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>162.394</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>37</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>28</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>227.848</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>39</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>28</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>215.712</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>41</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>28</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>218.498</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>43</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>28</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>238.406</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>45</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>38</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>470.73</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>47</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>38</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>379.334</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>49</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>46</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>156.616</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>51</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>28</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>190.718</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>53</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>28</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>190.718</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="45.375" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Width of basal phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1.1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>385.172</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1.1</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>426.144</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>5</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1.3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>154.5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1.3</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>243.48</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1.1</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>426.192</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>11</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>2.7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>472.78</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>13</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>2.7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>455.698</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>15</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>2.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>317.112</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>17</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1.1</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>332.858</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>19</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>1.1</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>358.578</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>21</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>1.3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>284.28</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>23</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>1.3</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>268.58</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>25</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>1.3</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>210.796</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>27</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>1.3</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>220.734</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>29</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>1.9</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>285.408</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>31</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1.3</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>182.462</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>33</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>1.3</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>184.032</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>35</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>1.3</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>159.002</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>37</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>1.3</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>226.524</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>39</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>1.3</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>209.55</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>41</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>1.3</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>211.78</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>43</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1.9</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>237.204</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>45</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>2.7</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>474.878</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>47</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>1.1</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>379.882</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>49</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>1.3</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>158.536</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>51</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>1.3</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>199.066</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>53</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>1.3</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>199.066</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="2" max="2" width="54.125" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Diameter of prismatic phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>23</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>383.334</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>3</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>4.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>427.644</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>5</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>20.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>155.502</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>9.5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>250.142</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>4.5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>428.216</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>11</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>463</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>13</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>23</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>450.766</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>15</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>28</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>315.32</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>17</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>23</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>329.956</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>19</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>28</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>355.85</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>21</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>286.042</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>23</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>4</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>271.06</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>25</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>6.5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>208.894</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>27</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>6.5</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>218.032</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>29</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>4</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>285.396</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>31</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>7</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>181.136</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>33</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>7</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>180.752</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>35</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>20.5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>162.214</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>37</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>6.5</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>230.86</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>39</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>6.5</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>214.578</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>41</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>6.5</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>216.594</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>43</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>242.34</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>45</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>6.5</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>467.532</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>47</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>23</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>377.938</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>49</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>7</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>157.986</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>51</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>12.5</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>191.038</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>53</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>12.5</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>191.038</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Diameter of basal phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
         <v>38</v>
       </c>
-      <c r="C2" t="n">
-        <v>385.6780000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C2">
+        <v>385.678</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>38</v>
       </c>
-      <c r="C3" t="n">
-        <v>432.6020000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3">
+        <v>432.602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>38</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>425.788</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>38</v>
       </c>
-      <c r="C5" t="n">
-        <v>435.1200000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C5">
+        <v>435.12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>26</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>156.616</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>27</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>170.15</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>28</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>245.698</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>28</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>229.028</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>38</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>426.27</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>38</v>
       </c>
-      <c r="C11" t="n">
-        <v>455.3380000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C11">
+        <v>455.338</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>38</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>467.756</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>38</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>492.11</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>38</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>447.672</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>38</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>452.698</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>10</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>315.606</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>10</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>335.028</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>38</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>332.804</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>26</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>358.044</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>26</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>360.058</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>26</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>359.848</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>28</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>283.13</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>28</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>257.302</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>28</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>267.886</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>28</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>194.532</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>28</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>210.768</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>28</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>198.84</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>28</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>219.028</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>28</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>285.58</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>28</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>279.72</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>28</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>275.906</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>27</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>183.366</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>34</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>190.022</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>38</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>182.002</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>28</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>184.628</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>26</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>162.394</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>28</v>
       </c>
-      <c r="C37" t="n">
-        <v>210.5820000000001</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="C37">
+        <v>210.582</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>28</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>227.848</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>28</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>197.528</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>28</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>215.712</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>28</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>217.08</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>28</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>218.498</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>28</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>218.612</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>28</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>238.406</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>38</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>431.87</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>38</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>470.73</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>38</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>486.904</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>38</v>
       </c>
-      <c r="C48" t="n">
-        <v>379.3340000000001</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="C48">
+        <v>379.334</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>28</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>180.532</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>46</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>156.616</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>28</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>197.912</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>28</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>190.718</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>28</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>197.912</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>28</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>190.718</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Width of basal phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>1.1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>385.172</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>1.1</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>433.262</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>1.1</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>426.144</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>1.1</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>435.188</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>1.3</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>154.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>1.3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>166.624</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>1.3</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>243.48</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>1.3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>224.142</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>1.1</v>
       </c>
-      <c r="C10" t="n">
-        <v>426.1920000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C10">
+        <v>426.192</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C11" t="n">
+      <c r="B11">
+        <v>2.7</v>
+      </c>
+      <c r="C11">
         <v>458.878</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C12" t="n">
-        <v>472.7800000000001</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="B12">
+        <v>2.7</v>
+      </c>
+      <c r="C12">
+        <v>472.78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C13" t="n">
+      <c r="B13">
+        <v>2.7</v>
+      </c>
+      <c r="C13">
         <v>503.91</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B14">
+        <v>2.7</v>
+      </c>
+      <c r="C14">
         <v>455.698</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C15" t="n">
+      <c r="B15">
+        <v>2.7</v>
+      </c>
+      <c r="C15">
         <v>460.22</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C16" t="n">
+      <c r="B16">
+        <v>2.7</v>
+      </c>
+      <c r="C16">
         <v>317.112</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>1.1</v>
       </c>
-      <c r="C17" t="n">
-        <v>335.3340000000001</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="C17">
+        <v>335.334</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>1.1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>332.858</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>1.1</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>356.508</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>1.1</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>358.578</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>1.1</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>358.34</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>1.3</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>284.28</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>1.3</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>257.2</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>1.3</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>268.58</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>1.3</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>190.76</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>1.3</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>210.796</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>1.3</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>201.998</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>1.3</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>220.734</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>1.9</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>287.214</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>1.9</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>285.408</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>1.9</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>281.31</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>1.3</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>182.462</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>1.3</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>190.688</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>1.3</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>184.032</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>1.3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>192.182</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>1.3</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>159.002</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>1.3</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>206.068</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>1.3</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>226.524</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>1.3</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>198.864</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>1.3</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>209.55</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>1.3</v>
       </c>
-      <c r="C41" t="n">
-        <v>210.4160000000001</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="C41">
+        <v>210.416</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>1.3</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>211.78</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>1.3</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>214.228</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>1.9</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>237.204</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C45" t="n">
-        <v>431.0520000000001</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="B45">
+        <v>2.7</v>
+      </c>
+      <c r="C45">
+        <v>431.052</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C46" t="n">
+      <c r="B46">
+        <v>2.7</v>
+      </c>
+      <c r="C46">
         <v>474.878</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
-        <v>2.699999999999999</v>
-      </c>
-      <c r="C47" t="n">
-        <v>500.4920000000001</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="B47">
+        <v>2.7</v>
+      </c>
+      <c r="C47">
+        <v>500.492</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>1.1</v>
       </c>
-      <c r="C48" t="n">
-        <v>379.8820000000001</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="C48">
+        <v>379.882</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>1.3</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>188.966</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>1.3</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>158.536</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>1.9</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>200.85</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>1.3</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>199.066</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>1.9</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>200.85</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>1.3</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>199.066</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Diameter of prismatic phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>23</v>
       </c>
-      <c r="C2" t="n">
-        <v>383.3340000000001</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C2">
+        <v>383.334</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>4.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>433.8440000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3">
+        <v>433.844</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>4.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>427.644</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>4.5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>436.378</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>20.5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>155.502</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>168.12</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>9.5</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>250.142</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>6.5</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>229.392</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>4.5</v>
       </c>
-      <c r="C10" t="n">
-        <v>428.2160000000001</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C10">
+        <v>428.216</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>4.5</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>452.796</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>9</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>463</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>9</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>501.088</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>23</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>450.766</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>9</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>456.698</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>28</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>315.32</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>23</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>331.812</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>23</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>329.956</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>28</v>
       </c>
-      <c r="C19" t="n">
-        <v>353.6600000000001</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="C19">
+        <v>353.66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>28</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>355.85</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>23</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>354.45</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>286.042</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>4</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>259.872</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>271.06</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>6.5</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>193.752</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>6.5</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>208.894</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>6.5</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>201.276</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>6.5</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>218.032</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>4</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>289.416</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>285.396</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>4</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>281.308</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>181.136</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>6.5</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>186.566</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>7</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>180.752</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>6.5</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>186.164</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>20.5</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>162.214</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>6.5</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>210.448</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>6.5</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>230.86</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>6.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>196.044</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>6.5</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>214.578</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>6.5</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>215.55</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>6.5</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>216.594</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>6.5</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>220.81</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>4</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>242.34</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>4.5</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>430.252</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>6.5</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>467.532</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>23</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>496.292</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>23</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>377.938</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>6.5</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>181.422</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>7</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>157.986</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>4</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>199.194</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>12.5</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>191.038</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>4</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>199.194</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>12.5</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>191.038</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="49.125" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Fraction of basal phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>5</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>386.678</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>7.5</v>
       </c>
-      <c r="C3" t="n">
-        <v>431.3320000000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3">
+        <v>431.332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>7.5</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>425.146</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>434.724</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>7</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>157.824</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>7</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>171.88</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>4.5</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>248.324</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>4.5</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>229.288</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>5</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>425.6</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>5</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>453.046</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>5</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>466</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>5</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>503.086</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>453.024</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>5</v>
       </c>
-      <c r="C15" t="n">
-        <v>459.3340000000001</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C15">
+        <v>459.334</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>5</v>
       </c>
-      <c r="C16" t="n">
-        <v>318.2620000000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="C16">
+        <v>318.262</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>5</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>337.482</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>334.72</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>5</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>358.388</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>5</v>
       </c>
-      <c r="C20" t="n">
-        <v>360.3919999999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="C20">
+        <v>360.392</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>5</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>360.144</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>4.5</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C22">
         <v>285.654</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>4.5</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>259.36</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>4.5</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>270.314</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>7</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>195.926</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>7</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>210.288</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>7</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>202.132</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>7</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>219.568</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>4.5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>288.938</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>4.5</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>283.372</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>4.5</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>281.072</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>7</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C32">
         <v>182.75</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>7</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>189.562</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>7</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>184.484</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>4.5</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>187.214</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>7</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>164.168</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>4.5</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>211.068</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>4.5</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>229.898</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>4.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>195.562</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>4.5</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>214.708</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>4.5</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>215.342</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>7</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>217.662</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>4.5</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>220.042</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>4.5</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>241.744</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>7.5</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>430.452</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>5</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>469.22</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>5</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>498.452</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>5</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>381.72</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>4.5</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>179.278</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>7</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>159.078</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>4.5</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>197.834</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>4.5</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>189.39</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>4.5</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>197.834</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>4.5</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>189.39</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+    <col min="2" max="2" width="54.125" customWidth="1"/>
+    <col min="3" max="3" width="30.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Track Number</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Fraction of prismatic phase with Max Change</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Predicted Yield Strength</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2">
         <v>12</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>365.54</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>12</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>430.514</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>12</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>422.892</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>12</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>433.066</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>13</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>156.458</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>13</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>172.014</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>9</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>246.522</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>9</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>227.356</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>12</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>424.436</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>15</v>
       </c>
-      <c r="C11" t="n">
-        <v>454.7640000000001</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C11">
+        <v>454.764</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>14</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>465.202</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>15</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>503.752</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>12</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>448.484</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>12</v>
       </c>
-      <c r="C15" t="n">
-        <v>454.6559999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C15">
+        <v>454.656</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>12</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>318.54</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>12</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>337.982</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>12</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>331.242</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>12</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>334.698</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>12</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>344.134</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>12</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>340.93</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>46</v>
       </c>
-      <c r="C22" t="n">
-        <v>287.9640000000001</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="C22">
+        <v>287.964</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>46</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C23">
         <v>265.842</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>46</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>276.89</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>9</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C25">
         <v>193.634</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>13</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26">
         <v>207.614</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>9</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C27">
         <v>199.402</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>13</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C28">
         <v>216.21</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C29">
         <v>290.316</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>3</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C30">
         <v>284.982</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>3</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C31">
         <v>280.884</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>13</v>
       </c>
-      <c r="C32" t="n">
-        <v>180.7080000000001</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="C32">
+        <v>180.708</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>13</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33">
         <v>189.894</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>33</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>13</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C34">
         <v>182.438</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>34</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>9</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C35">
         <v>189.558</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>35</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>9</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36">
         <v>163.524</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>36</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>9</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37">
         <v>208.432</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>37</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>9</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38">
         <v>229.62</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>38</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>9</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39">
         <v>196.408</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>39</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>9</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C40">
         <v>213.06</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>40</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>9</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C41">
         <v>217.43</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>41</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>9</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C42">
         <v>217.902</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>42</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>9</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C43">
         <v>220.28</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>43</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>3</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C44">
         <v>244.11</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>44</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>15</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C45">
         <v>429.556</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>45</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>15</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C46">
         <v>468.594</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>46</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>15</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C47">
         <v>500.774</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>47</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>12</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C48">
         <v>362.732</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>48</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>13</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C49">
         <v>183.092</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>49</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>13</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C50">
         <v>163.06</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>50</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>3</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C51">
         <v>201.71</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>51</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>9</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C52">
         <v>191.128</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>52</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>3</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C53">
         <v>201.71</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>53</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>9</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C54">
         <v>191.128</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>